--- a/data/trans_camb/IP19C07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 15,09</t>
+          <t>-11,12; 13,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 5,37</t>
+          <t>-18,91; 5,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 5,36</t>
+          <t>-16,95; 4,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 12,24</t>
+          <t>-11,7; 12,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 7,85</t>
+          <t>-13,83; 7,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 2,16</t>
+          <t>-16,2; 2,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 9,09</t>
+          <t>-8,18; 8,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 3,02</t>
+          <t>-13,54; 2,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 0,2</t>
+          <t>-13,93; -0,1</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 138,79</t>
+          <t>-47,27; 133,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 55,41</t>
+          <t>-84,81; 63,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,82; 59,06</t>
+          <t>-70,97; 44,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 157,45</t>
+          <t>-61,14; 153,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,63; 102,45</t>
+          <t>-70,67; 96,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,45; 33,23</t>
+          <t>-79,17; 38,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 78,15</t>
+          <t>-43,15; 75,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 27,25</t>
+          <t>-69,28; 29,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 3,8</t>
+          <t>-67,97; 0,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 11,83</t>
+          <t>-11,12; 11,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 9,5</t>
+          <t>-10,04; 9,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 16,15</t>
+          <t>-5,37; 15,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 16,07</t>
+          <t>-4,26; 15,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 0,94</t>
+          <t>-14,24; 0,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 9,92</t>
+          <t>-7,14; 10,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 10,73</t>
+          <t>-3,72; 10,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 3,27</t>
+          <t>-8,97; 3,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 10,62</t>
+          <t>-3,7; 10,54</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-64,52; 288,09</t>
+          <t>-70,54; 253,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,03; 206,86</t>
+          <t>-66,23; 239,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 325,99</t>
+          <t>-41,92; 352,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 828,54</t>
+          <t>-56,38; 709,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 540,03</t>
+          <t>-70,28; 553,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 230,82</t>
+          <t>-33,51; 218,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,01; 71,33</t>
+          <t>-74,15; 78,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,62; 221,82</t>
+          <t>-31,01; 223,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 11,36</t>
+          <t>-15,66; 11,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 7,64</t>
+          <t>-18,99; 7,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 4,1</t>
+          <t>-20,95; 5,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 8,24</t>
+          <t>-10,4; 6,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 2,43</t>
+          <t>-12,28; 2,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 17,01</t>
+          <t>-6,74; 16,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 6,14</t>
+          <t>-8,26; 6,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 2,84</t>
+          <t>-12,02; 3,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 7,65</t>
+          <t>-9,29; 7,48</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,67; 137,58</t>
+          <t>-67,86; 132,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-85,47; 92,41</t>
+          <t>-86,47; 88,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,5; 69,13</t>
+          <t>-90,25; 78,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-84,22; 253,69</t>
+          <t>-84,41; 189,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 111,55</t>
+          <t>-100,0; 146,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 323,35</t>
+          <t>-65,86; 337,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 78,81</t>
+          <t>-58,26; 91,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,13; 50,9</t>
+          <t>-79,61; 49,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,13; 95,67</t>
+          <t>-65,57; 98,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 3,4</t>
+          <t>-10,04; 3,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 2,62</t>
+          <t>-9,86; 2,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 1,71</t>
+          <t>-10,51; 1,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -2,69</t>
+          <t>-16,17; -3,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -0,66</t>
+          <t>-14,55; -1,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -2,58</t>
+          <t>-16,7; -3,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,02; -2,02</t>
+          <t>-10,8; -1,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -0,97</t>
+          <t>-10,6; -1,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,71; -2,66</t>
+          <t>-11,55; -2,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,59; 65,51</t>
+          <t>-74,55; 61,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,45; 57,44</t>
+          <t>-76,66; 38,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,97; 40,89</t>
+          <t>-79,9; 33,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,2; -24,81</t>
+          <t>-87,79; -28,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,96; -2,4</t>
+          <t>-80,71; -4,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,85; -13,42</t>
+          <t>-89,71; -21,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,97; -19,93</t>
+          <t>-74,54; -12,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,25; -8,98</t>
+          <t>-71,68; -14,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-79,42; -22,96</t>
+          <t>-78,79; -25,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 0,89</t>
+          <t>-12,63; 1,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 11,41</t>
+          <t>-5,93; 11,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 4,2</t>
+          <t>-9,96; 4,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 13,67</t>
+          <t>-2,29; 14,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,24</t>
+          <t>-6,92; 6,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 1,37</t>
+          <t>-9,39; 1,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 5,61</t>
+          <t>-4,86; 5,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,54</t>
+          <t>-4,09; 6,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,9</t>
+          <t>-7,72; 1,24</t>
         </is>
       </c>
     </row>
@@ -1652,42 +1652,42 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 330,94</t>
+          <t>-53,65; 311,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,03; 163,08</t>
+          <t>-83,37; 177,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 575,49</t>
+          <t>-37,11; 539,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 278,94</t>
+          <t>-77,66; 260,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 149,23</t>
+          <t>-53,77; 133,6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 162,88</t>
+          <t>-44,85; 161,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,49; 29,46</t>
+          <t>-80,52; 38,63</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 15,57</t>
+          <t>-16,58; 17,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 1,68</t>
+          <t>-24,04; 1,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-28,41; -5,95</t>
+          <t>-29,09; -5,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 27,58</t>
+          <t>0,76; 26,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 12,72</t>
+          <t>-9,94; 13,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 5,29</t>
+          <t>-12,44; 5,73</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 16,19</t>
+          <t>-5,67; 15,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 3,15</t>
+          <t>-14,75; 3,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,36; -3,46</t>
+          <t>-18,74; -2,93</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 113,9</t>
+          <t>-64,26; 110,94</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,12; 29,65</t>
+          <t>-88,93; 18,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,35</t>
+          <t>-100,0; -9,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 1040,79</t>
+          <t>-15,87; 1134,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 580,87</t>
+          <t>-86,52; 518,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 154,39</t>
+          <t>-30,77; 158,64</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 44,27</t>
+          <t>-75,92; 46,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -18,52</t>
+          <t>-100,0; -13,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 1,03</t>
+          <t>-6,68; 1,23</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -0,54</t>
+          <t>-7,55; 0,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -0,99</t>
+          <t>-8,81; -0,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,35</t>
+          <t>-3,38; 3,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -0,65</t>
+          <t>-7,19; -0,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,7; -1,14</t>
+          <t>-7,22; -1,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,58</t>
+          <t>-4,03; 1,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -1,23</t>
+          <t>-6,58; -1,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -2,17</t>
+          <t>-7,37; -2,42</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 10,63</t>
+          <t>-45,18; 11,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,61; -4,97</t>
+          <t>-51,56; 1,11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,55; -8,53</t>
+          <t>-59,42; -6,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 53,78</t>
+          <t>-30,25; 43,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-61,06; -7,58</t>
+          <t>-60,26; -7,1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-63,39; -12,31</t>
+          <t>-61,88; -11,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 15,9</t>
+          <t>-31,17; 15,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-50,83; -11,65</t>
+          <t>-51,03; -12,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-55,91; -22,49</t>
+          <t>-57,96; -23,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 13,86</t>
+          <t>-12,32; 13,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 5,95</t>
+          <t>-18,53; 4,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 4,72</t>
+          <t>-17,57; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 12,98</t>
+          <t>-12,68; 11,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 7,27</t>
+          <t>-14,4; 8,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 2,29</t>
+          <t>-17,23; 2,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 8,94</t>
+          <t>-8,63; 9,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 2,84</t>
+          <t>-13,83; 2,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -0,1</t>
+          <t>-13,89; 0,38</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 133,67</t>
+          <t>-52,98; 115,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,81; 63,74</t>
+          <t>-83,96; 46,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,97; 44,42</t>
+          <t>-74,81; 46,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,14; 153,75</t>
+          <t>-62,97; 129,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,67; 96,1</t>
+          <t>-71,2; 123,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 38,48</t>
+          <t>-80,09; 33,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 75,87</t>
+          <t>-44,3; 79,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,28; 29,43</t>
+          <t>-69,89; 27,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 0,11</t>
+          <t>-67,7; 6,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 11,12</t>
+          <t>-9,33; 12,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 9,46</t>
+          <t>-11,41; 9,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 15,95</t>
+          <t>-5,73; 16,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 15,0</t>
+          <t>-4,6; 15,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 0,11</t>
+          <t>-14,94; 0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 10,15</t>
+          <t>-8,19; 10,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 10,41</t>
+          <t>-4,57; 11,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,36</t>
+          <t>-9,13; 3,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 10,54</t>
+          <t>-3,72; 10,56</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 253,47</t>
+          <t>-61,09; 315,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,23; 239,82</t>
+          <t>-70,28; 203,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 352,48</t>
+          <t>-44,26; 365,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 709,17</t>
+          <t>-60,94; 848,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 553,4</t>
+          <t>-70,27; inf</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 218,44</t>
+          <t>-37,85; 260,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 78,1</t>
+          <t>-73,36; 92,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 223,26</t>
+          <t>-31,7; 236,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 11,33</t>
+          <t>-17,39; 9,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 7,49</t>
+          <t>-20,64; 7,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 5,55</t>
+          <t>-22,04; 5,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 6,85</t>
+          <t>-10,61; 6,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 2,95</t>
+          <t>-12,44; 2,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 16,82</t>
+          <t>-7,46; 16,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 6,62</t>
+          <t>-9,04; 5,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 3,24</t>
+          <t>-11,44; 2,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 7,48</t>
+          <t>-9,55; 8,93</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 132,37</t>
+          <t>-72,55; 115,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 88,1</t>
+          <t>-83,39; 97,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,25; 78,27</t>
+          <t>-90,4; 104,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-84,41; 189,79</t>
+          <t>-83,53; 187,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,19</t>
+          <t>-100,0; 143,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 337,44</t>
+          <t>-68,66; 364,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,26; 91,22</t>
+          <t>-59,62; 80,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,61; 49,77</t>
+          <t>-78,52; 44,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,57; 98,74</t>
+          <t>-62,71; 116,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 3,08</t>
+          <t>-9,94; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 2,19</t>
+          <t>-10,16; 2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 1,4</t>
+          <t>-10,7; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -3,26</t>
+          <t>-16,39; -3,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -1,42</t>
+          <t>-14,62; -0,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -3,41</t>
+          <t>-16,47; -2,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -1,5</t>
+          <t>-10,8; -1,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -1,69</t>
+          <t>-10,31; -1,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,55; -2,89</t>
+          <t>-11,72; -2,78</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 61,43</t>
+          <t>-70,7; 66,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,66; 38,25</t>
+          <t>-76,52; 50,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,9; 33,83</t>
+          <t>-81,49; 30,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-87,79; -28,04</t>
+          <t>-86,75; -26,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,71; -4,54</t>
+          <t>-79,79; -2,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,71; -21,37</t>
+          <t>-89,98; -18,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,54; -12,49</t>
+          <t>-73,79; -20,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-71,68; -14,06</t>
+          <t>-71,75; -12,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-78,79; -25,93</t>
+          <t>-80,34; -26,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 1,62</t>
+          <t>-12,34; 1,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 11,12</t>
+          <t>-5,77; 10,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 4,71</t>
+          <t>-10,03; 4,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 14,04</t>
+          <t>-1,6; 14,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 6,13</t>
+          <t>-6,05; 6,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 1,47</t>
+          <t>-9,12; 1,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 5,38</t>
+          <t>-4,97; 5,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 6,39</t>
+          <t>-3,94; 6,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 1,24</t>
+          <t>-7,7; 1,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,62; 129,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,65; 311,33</t>
+          <t>-53,44; 292,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,37; 177,58</t>
+          <t>-88,32; 145,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 539,79</t>
+          <t>-32,0; 528,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,66; 260,54</t>
+          <t>-71,24; 255,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 103,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-53,77; 133,6</t>
+          <t>-52,7; 144,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 161,41</t>
+          <t>-45,23; 184,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 38,63</t>
+          <t>-82,08; 37,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 17,52</t>
+          <t>-17,6; 15,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 1,65</t>
+          <t>-25,69; 2,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-29,09; -5,09</t>
+          <t>-29,37; -5,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,76; 26,81</t>
+          <t>1,55; 27,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 13,04</t>
+          <t>-9,31; 12,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 5,73</t>
+          <t>-11,08; 5,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 15,79</t>
+          <t>-3,99; 16,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 3,78</t>
+          <t>-14,19; 3,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,74; -2,93</t>
+          <t>-17,71; -2,81</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 110,94</t>
+          <t>-67,26; 142,03</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 18,1</t>
+          <t>-89,73; 31,07</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,84</t>
+          <t>-100,0; -0,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 1134,51</t>
+          <t>-5,69; 1044,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-86,52; 518,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 158,64</t>
+          <t>-22,95; 171,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-75,92; 46,05</t>
+          <t>-77,83; 38,6</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,21</t>
+          <t>-93,87; -0,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,23</t>
+          <t>-6,95; 1,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,07</t>
+          <t>-8,1; -0,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -0,73</t>
+          <t>-8,34; -1,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,78</t>
+          <t>-3,75; 4,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -0,64</t>
+          <t>-7,33; -0,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -1,02</t>
+          <t>-7,6; -0,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,52</t>
+          <t>-4,05; 1,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -1,27</t>
+          <t>-6,52; -1,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,42</t>
+          <t>-7,3; -2,27</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,18; 11,0</t>
+          <t>-45,2; 13,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 1,11</t>
+          <t>-54,62; -2,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,42; -6,49</t>
+          <t>-57,42; -11,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 43,08</t>
+          <t>-30,87; 52,85</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,26; -7,1</t>
+          <t>-60,84; -5,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-61,88; -11,45</t>
+          <t>-63,14; -9,32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 15,3</t>
+          <t>-31,1; 18,97</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-51,03; -12,85</t>
+          <t>-51,74; -11,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,96; -23,32</t>
+          <t>-56,55; -22,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C07-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C07-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,41</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-7,74</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,36</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,41</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>-6,25</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 13,73</t>
+          <t>-11,39; 12,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 4,97</t>
+          <t>-15,2; 7,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 4,03</t>
+          <t>-16,53; 3,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 11,37</t>
+          <t>-10,65; 15,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 8,66</t>
+          <t>-19,46; 5,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 2,1</t>
+          <t>-15,72; 7,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 9,46</t>
+          <t>-8,23; 9,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 2,98</t>
+          <t>-13,08; 3,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 0,38</t>
+          <t>-13,61; 1,01</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-0,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-24,19%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-43,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-44,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-36,33%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,26%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-24,19%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-47,04%</t>
+          <t>-32,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-43,11%</t>
+          <t>-39,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 115,33</t>
+          <t>-60,42; 157,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,96; 46,53</t>
+          <t>-71,63; 102,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,81; 46,11</t>
+          <t>-76,59; 46,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,97; 129,85</t>
+          <t>-48,02; 138,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 123,5</t>
+          <t>-82,38; 55,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,09; 33,6</t>
+          <t>-68,62; 68,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 79,92</t>
+          <t>-41,04; 78,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,89; 27,47</t>
+          <t>-66,1; 27,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 6,91</t>
+          <t>-66,91; 11,88</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,8</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,45</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,11</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,37</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,49</t>
+          <t>3,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 12,99</t>
+          <t>-4,26; 16,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 9,22</t>
+          <t>-15,03; 0,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 16,03</t>
+          <t>-6,98; 10,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 15,42</t>
+          <t>-9,7; 11,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 0,68</t>
+          <t>-10,76; 9,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 10,44</t>
+          <t>-6,03; 15,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 11,18</t>
+          <t>-4,15; 10,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 3,43</t>
+          <t>-9,88; 3,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 10,56</t>
+          <t>-4,0; 10,62</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-78,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,38%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-1,13%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-78,15%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,09; 315,69</t>
+          <t>-54,41; 828,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 203,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 365,83</t>
+          <t>-71,08; 567,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 848,11</t>
+          <t>-64,52; 288,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,03; 206,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,27; inf</t>
+          <t>-40,57; 318,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 260,94</t>
+          <t>-33,86; 230,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 92,71</t>
+          <t>-76,01; 71,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 236,28</t>
+          <t>-35,68; 224,67</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,04</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,86</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-6,22</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-8,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-5,0</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>-8,66</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 9,69</t>
+          <t>-10,72; 8,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 7,2</t>
+          <t>-12,52; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 5,29</t>
+          <t>-6,11; 19,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 6,52</t>
+          <t>-15,56; 11,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 2,49</t>
+          <t>-19,82; 7,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 16,51</t>
+          <t>-22,35; 4,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 5,5</t>
+          <t>-9,19; 6,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 2,64</t>
+          <t>-12,4; 2,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 8,93</t>
+          <t>-9,23; 8,01</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-23,85%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-58,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-17,71%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-37,77%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-51,63%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-23,85%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-58,42%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>-52,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,71%</t>
+          <t>-11,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-72,55; 115,13</t>
+          <t>-84,22; 253,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 97,04</t>
+          <t>-100,0; 111,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,4; 104,9</t>
+          <t>-58,92; 361,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,53; 187,35</t>
+          <t>-67,67; 137,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,52</t>
+          <t>-85,47; 92,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 364,98</t>
+          <t>-90,39; 76,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,62; 80,6</t>
+          <t>-59,49; 78,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,52; 44,22</t>
+          <t>-80,13; 50,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 116,91</t>
+          <t>-62,4; 96,76</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-9,5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-7,89</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-9,67</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-9,5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,89</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,87</t>
+          <t>-4,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,13</t>
+          <t>-6,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 2,98</t>
+          <t>-16,34; -2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 2,66</t>
+          <t>-14,39; -0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 1,36</t>
+          <t>-15,77; -2,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,39; -3,11</t>
+          <t>-8,67; 3,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -0,6</t>
+          <t>-10,06; 2,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,47; -2,67</t>
+          <t>-10,43; 2,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -1,9</t>
+          <t>-11,02; -2,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -1,43</t>
+          <t>-10,45; -0,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,72; -2,78</t>
+          <t>-11,62; -2,42</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-67,15%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-55,79%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-68,37%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-30,96%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-38,35%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-46,85%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-67,15%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-55,79%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-69,8%</t>
+          <t>-44,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-60,78%</t>
+          <t>-58,86%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,7; 66,93</t>
+          <t>-87,2; -24,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,52; 50,63</t>
+          <t>-80,96; -2,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,49; 30,74</t>
+          <t>-88,01; -10,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-86,75; -26,44</t>
+          <t>-68,59; 65,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,79; -2,79</t>
+          <t>-73,45; 57,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,98; -18,23</t>
+          <t>-77,27; 45,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-73,79; -20,07</t>
+          <t>-74,97; -19,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-71,75; -12,1</t>
+          <t>-74,25; -8,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,34; -26,31</t>
+          <t>-79,04; -19,8</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,35</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,22</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-4,33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,93</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-2,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,04</t>
+          <t>-2,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 1,39</t>
+          <t>-2,08; 13,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 10,92</t>
+          <t>-6,56; 7,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 4,57</t>
+          <t>-8,97; 1,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 14,14</t>
+          <t>-12,43; 0,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 6,81</t>
+          <t>-5,19; 11,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 1,58</t>
+          <t>-10,17; 4,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 5,44</t>
+          <t>-4,98; 5,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 6,94</t>
+          <t>-3,8; 6,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 1,31</t>
+          <t>-7,84; 1,19</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,29%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-54,81%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-57,24%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-31,89%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-1,29%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-57,04%</t>
+          <t>-28,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-45,99%</t>
+          <t>-42,29%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-91,62; 129,13</t>
+          <t>-33,16; 575,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,44; 292,7</t>
+          <t>-76,7; 278,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,32; 145,14</t>
+          <t>-100,0; 123,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 528,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,24; 255,0</t>
+          <t>-55,19; 330,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,37</t>
+          <t>-87,54; 188,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 144,41</t>
+          <t>-55,42; 149,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 184,11</t>
+          <t>-42,16; 162,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 37,66</t>
+          <t>-80,6; 37,98</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>13,35</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-3,03</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-1,48</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-11,46</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-17,51</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>13,35</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-17,31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-10,68</t>
+          <t>-10,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 15,67</t>
+          <t>0,15; 27,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 2,27</t>
+          <t>-8,59; 12,72</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-29,37; -5,08</t>
+          <t>-11,15; 5,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,55; 27,62</t>
+          <t>-17,43; 15,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 12,03</t>
+          <t>-25,24; 1,68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 5,31</t>
+          <t>-28,28; -5,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 16,84</t>
+          <t>-3,58; 16,19</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 3,3</t>
+          <t>-14,07; 3,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -2,81</t>
+          <t>-18,22; -3,01</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>181,89%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-41,27%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-7,2%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-55,74%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-85,15%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>181,89%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>18,37%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-42,24%</t>
+          <t>-84,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-74,58%</t>
+          <t>-73,75%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-67,26; 142,03</t>
+          <t>-15,19; 1040,79</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 31,07</t>
+          <t>-79,6; 580,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1044,85</t>
+          <t>-65,23; 113,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,12; 29,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 9,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 171,86</t>
+          <t>-22,7; 154,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 38,6</t>
+          <t>-74,55; 44,27</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-93,87; -0,36</t>
+          <t>-100,0; -16,04</t>
         </is>
       </c>
     </row>
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-3,99</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-3,98</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-2,71</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,05</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,85</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-4,65</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-1,16</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>-3,99</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-4,28</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-3,99</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,64</t>
+          <t>-4,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 1,37</t>
+          <t>-3,11; 4,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,1; -0,34</t>
+          <t>-7,3; -0,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -1,23</t>
+          <t>-7,38; -0,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 4,16</t>
+          <t>-7,74; 1,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,49</t>
+          <t>-8,69; -0,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -0,94</t>
+          <t>-8,64; -0,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,84</t>
+          <t>-3,93; 1,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -1,17</t>
+          <t>-6,44; -1,23</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -2,27</t>
+          <t>-6,82; -1,9</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-39,97%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-39,88%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-21,35%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-31,91%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-38,18%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-39,97%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-42,8%</t>
+          <t>-36,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-41,02%</t>
+          <t>-38,54%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 13,42</t>
+          <t>-27,54; 53,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-54,62; -2,0</t>
+          <t>-61,06; -7,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,42; -11,87</t>
+          <t>-61,3; -8,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 52,85</t>
+          <t>-49,18; 10,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,84; -5,91</t>
+          <t>-56,61; -4,97</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-63,14; -9,32</t>
+          <t>-57,9; -6,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 18,97</t>
+          <t>-30,21; 15,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-51,74; -11,93</t>
+          <t>-50,83; -11,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,55; -22,97</t>
+          <t>-54,14; -19,99</t>
         </is>
       </c>
     </row>
